--- a/servers/maze_main_server/conf.d/data/maze_bag_order_v8【迷宫-背包-物品排序】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_bag_order_v8【迷宫-背包-物品排序】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BB9B18-164C-494D-9A5F-01D7134C210A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AA80C8-3638-482B-8307-E2597A77FCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_bag_order_v8" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -70,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -120,6 +118,18 @@
   <si>
     <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命药剂</t>
+  </si>
+  <si>
+    <t>强化水晶</t>
+  </si>
+  <si>
+    <t>塑造精华</t>
+  </si>
+  <si>
+    <t>体力药剂</t>
   </si>
 </sst>
 </file>
@@ -487,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -567,6 +577,62 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>43400002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>46700001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>46800001</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>49000001</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
